--- a/rpa_workflow/Data/Master_Log.xlsx
+++ b/rpa_workflow/Data/Master_Log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <x:si>
     <x:t>분석일시</x:t>
   </x:si>
@@ -242,6 +242,207 @@
   </x:si>
   <x:si>
     <x:t>2026-06-11 22:11:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:10:51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: Error code: 401 - {'err</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: Error code: 401 - {'error': {'message': 'Incorrect API key provided: sk-xxxxx. You can find your API key at https://platform.openai.com/account/api-keys.', 'type': 'invalid_request_error', 'code': 'invalid_api_key', 'param': None}, 'status': 401}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흠... 벨먼꺼 너무 좋아하는데 너무 기대했나봐요 .. 화이트머스크로 다시 구입할라구요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.06.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:12:19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:12:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:22:51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:22:52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:28:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:37:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스크럽 알갱이가 있어서 데일리로 사용하기 좋은 제품이에요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.05.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판매자에게 제품비 일부를 지원받았지만, 저의 솔직한 후기입니다. 벨먼 스크럽워시 사용해봤어요! 스크럽입자는 두껍고 거칠지않고 잔잔한 편이에요 바닐라향이 많이나서 바닐라 쿠앤크 아이스크림을 몸에 문지르는 느낌?괄사 컵도 너무 기엽고 유용해서 좋아요 ㅎㅎ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>향도좋고 다 좋은데 쓰다보면 잘 안나와요 ㅠ 너무 꾸덕해서 그런지..ㅠ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.06.14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남친이 추천해줘서 써봣는데 향 ㅈㅉ좋아요 제 혈육이 향에 민감하고 까탈시러운데 써보더니 향 좋다구 잘 삿다구하네여</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026.06.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 15:41:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:09:26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: GEMINI_API_KEY 미설정. ai_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: GEMINI_API_KEY 미설정. ai_server/.env 에 키를 넣으세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:12:58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:15:58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: 404 models/gpt-5.4-mini</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: 404 models/gpt-5.4-mini is not found for API version v1beta, or is not supported for generateContent. Call ModelService.ListModels to see the list of available models and their supported methods.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:22:27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: module 'google.genai' h</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: module 'google.genai' has no attribute 'configure'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:26:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: 429 RESOURCE_EXHAUSTED.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_input_token_count, limit: 0, model: gemini-2.0-flash\n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 0, model: gemini-2.0-flash\n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 0, model: gemini-2.0-flash\nPlease retry in 28.872451972s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_input_token_count', 'quotaId': 'GenerateContentInputTokensPerModelPerMinute-FreeTier', 'quotaDimensions': {'model': 'gemini-2.0-flash', 'location': 'global'}}, {'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.0-flash'}}, {'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerDayPerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.0-flash'}}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '28s'}]}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:26:31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:29:36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: 404 NOT_FOUND. {'error'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: 404 NOT_FOUND. {'error': {'code': 404, 'message': 'models/gemini-2.5-flash-lite-preview-06-17 is not found for API version v1beta, or is not supported for generateContent. Call ModelService.ListModels to see the list of available models and their supported methods.', 'status': 'NOT_FOUND'}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:31:54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:34:55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리 오류: 'list' object has no at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미분류 처리: 처리 오류: 'list' object has no attribute 'get'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:39:26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긍정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고보습 스크럽워시, 부드러운 제형, 힐링 향</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마케팅팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰 텍스트 전반에 걸쳐 제품의 향, 제형, 사용감에 대한 긍정적인 내용만 담겨 있습니다. 특별한 불만이나 결함이 언급되지 않았습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 제형, 훌륭한 바닐라 향</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰어는 제품의 부드러운 제형과 매우 만족스러운 바닐라 향을 강조하며, 바디미스트 출시를 희망할 정도로 긍정적인 경험을 공유했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스크럽 알갱이, 데일리 사용 적합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리뷰는 스크럽 알갱이가 있어 매일 사용하기 좋다는 내용으로, 제품에 대한 긍정적인 평가입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품결함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>펌핑 불량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>품질관리팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>high</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용물은 좋으나 펌핑이 되지 않아 제품을 사용할 수 없는 명백한 결함(작동 불량)을 언급하고 있어 제품결함으로 분류합니다. 이는 즉시 대응이 필요한 사항입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 스크럽, 풍성한 거품, 선호 향</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스크럽이 있지만 부드럽고 자극이 없으며, 향도 선호하는 편이라는 긍정적인 내용입니다. 괄사는 '의미가 없는 증정품'으로 평가했으나, 제품 자체에 대한 불만은 아닙니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보습감 있는 제형, 은은한 바닐라 머스크 향</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기존 제품보다 보습감이 좋고, 바닐라 머스크 향이 은은하다는 긍정적인 평가입니다. 향에 대한 호불호 가능성을 언급했지만, 제품 자체의 결함이나 심각한 불만은 아닙니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 스크럽 입자, 기여운 괄사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스크럽 입자가 두껍지 않고 잔잔하며, 괄사 컵도 귀엽고 유용하다고 긍정적으로 평가하고 있습니다. 판매자 지원 리뷰이지만 솔직한 후기임을 명시했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러운 향, 우수한 보습력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바닐라 머스크 향이 은은하고 오래가며, 샤워 후 더 부드럽고 알갱이도 거칠지 않아 매일 사용하기 좋다는 긍정적인 리뷰입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용물이 잘 안 나옴, 너무 꾸덕함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품의 향 등은 좋다고 언급했으나, '쓰다 보면 잘 안 나온다', '너무 꾸덕해서'라는 사용상의 불편함을 표현하고 있습니다. 이는 제품 결함으로 보기에는 다소 애매하지만, 개선이 필요한 부분으로 단순불만으로 분류했습니다. 확신도는 중간입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 향, 만족스러운 추천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주변 추천으로 사용해본 결과 향이 매우 좋으며, 타인에게도 좋은 평가를 받았다는 내용으로 긍정적인 리뷰입니다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3673,6 +3874,5706 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
+    <x:row r="82" spans="1:12">
+      <x:c r="A82" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L82" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:12">
+      <x:c r="A83" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H83" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J83" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L83" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:12">
+      <x:c r="A84" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H84" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J84" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K84" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L84" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:12">
+      <x:c r="A85" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H85" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K85" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L85" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:12">
+      <x:c r="A86" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H86" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J86" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K86" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L86" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:12">
+      <x:c r="A87" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J87" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L87" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:12">
+      <x:c r="A88" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J88" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K88" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L88" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:12">
+      <x:c r="A89" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J89" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L89" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:12">
+      <x:c r="A90" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J90" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K90" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L90" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:12">
+      <x:c r="A91" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H91" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J91" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K91" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L91" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:12">
+      <x:c r="A92" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J92" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K92" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L92" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:12">
+      <x:c r="A93" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J93" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K93" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L93" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:12">
+      <x:c r="A94" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J94" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K94" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L94" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:12">
+      <x:c r="A95" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G95" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J95" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L95" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:12">
+      <x:c r="A96" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G96" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J96" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L96" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:12">
+      <x:c r="A97" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G97" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J97" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L97" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:12">
+      <x:c r="A98" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G98" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J98" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L98" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:12">
+      <x:c r="A99" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G99" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J99" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L99" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:12">
+      <x:c r="A100" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G100" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J100" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L100" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:12">
+      <x:c r="A101" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G101" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J101" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L101" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:12">
+      <x:c r="A102" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G102" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H102" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I102" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J102" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K102" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L102" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:12">
+      <x:c r="A103" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G103" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H103" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I103" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J103" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K103" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L103" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:12">
+      <x:c r="A104" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F104" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G104" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H104" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I104" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J104" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K104" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L104" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:12">
+      <x:c r="A105" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G105" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H105" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I105" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J105" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L105" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:12">
+      <x:c r="A106" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G106" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H106" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I106" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J106" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L106" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:12">
+      <x:c r="A107" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G107" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H107" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I107" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J107" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L107" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:12">
+      <x:c r="A108" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G108" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H108" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I108" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J108" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K108" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L108" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:12">
+      <x:c r="A109" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G109" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H109" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I109" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J109" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K109" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L109" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:12">
+      <x:c r="A110" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G110" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H110" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I110" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J110" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K110" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L110" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:12">
+      <x:c r="A111" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F111" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G111" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H111" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I111" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J111" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K111" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L111" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:12">
+      <x:c r="A112" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G112" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H112" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I112" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J112" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L112" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:12">
+      <x:c r="A113" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G113" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H113" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I113" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J113" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L113" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:12">
+      <x:c r="A114" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E114" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G114" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H114" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I114" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J114" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K114" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L114" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:12">
+      <x:c r="A115" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E115" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G115" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H115" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I115" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J115" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L115" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:12">
+      <x:c r="A116" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G116" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H116" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I116" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J116" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K116" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L116" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:12">
+      <x:c r="A117" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G117" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H117" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I117" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J117" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K117" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L117" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:12">
+      <x:c r="A118" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G118" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H118" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I118" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J118" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K118" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L118" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:12">
+      <x:c r="A119" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G119" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H119" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I119" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J119" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K119" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L119" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:12">
+      <x:c r="A120" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G120" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H120" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I120" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J120" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K120" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L120" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:12">
+      <x:c r="A121" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G121" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H121" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I121" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J121" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K121" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L121" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:12">
+      <x:c r="A122" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F122" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G122" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H122" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I122" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J122" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K122" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L122" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:12">
+      <x:c r="A123" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G123" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H123" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I123" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J123" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K123" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L123" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:12">
+      <x:c r="A124" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F124" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G124" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H124" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I124" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J124" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K124" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L124" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:12">
+      <x:c r="A125" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G125" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H125" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I125" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J125" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K125" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L125" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:12">
+      <x:c r="A126" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G126" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H126" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I126" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J126" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L126" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:12">
+      <x:c r="A127" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G127" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H127" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I127" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J127" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L127" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:12">
+      <x:c r="A128" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G128" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H128" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I128" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J128" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K128" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L128" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:12">
+      <x:c r="A129" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G129" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H129" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I129" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J129" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L129" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:12">
+      <x:c r="A130" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G130" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H130" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I130" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J130" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L130" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:12">
+      <x:c r="A131" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G131" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H131" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I131" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J131" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K131" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L131" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:12">
+      <x:c r="A132" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G132" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H132" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I132" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J132" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K132" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L132" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:12">
+      <x:c r="A133" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G133" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H133" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I133" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J133" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K133" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L133" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:12">
+      <x:c r="A134" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G134" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H134" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I134" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J134" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L134" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:12">
+      <x:c r="A135" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F135" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G135" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H135" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I135" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J135" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K135" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L135" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:12">
+      <x:c r="A136" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F136" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G136" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H136" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I136" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J136" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K136" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L136" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:12">
+      <x:c r="A137" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G137" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H137" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I137" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J137" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K137" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L137" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:12">
+      <x:c r="A138" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G138" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H138" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I138" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J138" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L138" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:12">
+      <x:c r="A139" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F139" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G139" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H139" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I139" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J139" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K139" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L139" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:12">
+      <x:c r="A140" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F140" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G140" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H140" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I140" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J140" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K140" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L140" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:12">
+      <x:c r="A141" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G141" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H141" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I141" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J141" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K141" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L141" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:12">
+      <x:c r="A142" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F142" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G142" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H142" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I142" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J142" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K142" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L142" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:12">
+      <x:c r="A143" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F143" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G143" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H143" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I143" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J143" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K143" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L143" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:12">
+      <x:c r="A144" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F144" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G144" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H144" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I144" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J144" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L144" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:12">
+      <x:c r="A145" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G145" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H145" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I145" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J145" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K145" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L145" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:12">
+      <x:c r="A146" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G146" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H146" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I146" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J146" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K146" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L146" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:12">
+      <x:c r="A147" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F147" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G147" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H147" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I147" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J147" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K147" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L147" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:12">
+      <x:c r="A148" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F148" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G148" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H148" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I148" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J148" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K148" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L148" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:12">
+      <x:c r="A149" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G149" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H149" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I149" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J149" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K149" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L149" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:12">
+      <x:c r="A150" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G150" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H150" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I150" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J150" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K150" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L150" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:12">
+      <x:c r="A151" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F151" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G151" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H151" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I151" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J151" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K151" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L151" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:12">
+      <x:c r="A152" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F152" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G152" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H152" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I152" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J152" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K152" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L152" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:12">
+      <x:c r="A153" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F153" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G153" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H153" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I153" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J153" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K153" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L153" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:12">
+      <x:c r="A154" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E154" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F154" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G154" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H154" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I154" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J154" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K154" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L154" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:12">
+      <x:c r="A155" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F155" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G155" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H155" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I155" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J155" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K155" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L155" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:12">
+      <x:c r="A156" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G156" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H156" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I156" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J156" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K156" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L156" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:12">
+      <x:c r="A157" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F157" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G157" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H157" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I157" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J157" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K157" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L157" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:12">
+      <x:c r="A158" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G158" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H158" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I158" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J158" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K158" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L158" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:12">
+      <x:c r="A159" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G159" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H159" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I159" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J159" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K159" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L159" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:12">
+      <x:c r="A160" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G160" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H160" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I160" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J160" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K160" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L160" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:12">
+      <x:c r="A161" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G161" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H161" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I161" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J161" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K161" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L161" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:12">
+      <x:c r="A162" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F162" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G162" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H162" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I162" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J162" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K162" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L162" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:12">
+      <x:c r="A163" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F163" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G163" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H163" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I163" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J163" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K163" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L163" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:12">
+      <x:c r="A164" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F164" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G164" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H164" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I164" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J164" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K164" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L164" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:12">
+      <x:c r="A165" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F165" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G165" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H165" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I165" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J165" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K165" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L165" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:12">
+      <x:c r="A166" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F166" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G166" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H166" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I166" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J166" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K166" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L166" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:12">
+      <x:c r="A167" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F167" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G167" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H167" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I167" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J167" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K167" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L167" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:12">
+      <x:c r="A168" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G168" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H168" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I168" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J168" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K168" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L168" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:12">
+      <x:c r="A169" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G169" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H169" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I169" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J169" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K169" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L169" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:12">
+      <x:c r="A170" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G170" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H170" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I170" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J170" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K170" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L170" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:12">
+      <x:c r="A171" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G171" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H171" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I171" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J171" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K171" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L171" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:12">
+      <x:c r="A172" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G172" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H172" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I172" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J172" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K172" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L172" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:12">
+      <x:c r="A173" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G173" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H173" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I173" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J173" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K173" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L173" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:12">
+      <x:c r="A174" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G174" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H174" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I174" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J174" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K174" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L174" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:12">
+      <x:c r="A175" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G175" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H175" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I175" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J175" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K175" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L175" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:12">
+      <x:c r="A176" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G176" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H176" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I176" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J176" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K176" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L176" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:12">
+      <x:c r="A177" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G177" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H177" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I177" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J177" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K177" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L177" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:12">
+      <x:c r="A178" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F178" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G178" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H178" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I178" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J178" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K178" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L178" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:12">
+      <x:c r="A179" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F179" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G179" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H179" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I179" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J179" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K179" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L179" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:12">
+      <x:c r="A180" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E180" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G180" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H180" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I180" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J180" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K180" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L180" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:12">
+      <x:c r="A181" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F181" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G181" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H181" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I181" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J181" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K181" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L181" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:12">
+      <x:c r="A182" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F182" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G182" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H182" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I182" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J182" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K182" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L182" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:12">
+      <x:c r="A183" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G183" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H183" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I183" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J183" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K183" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L183" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:12">
+      <x:c r="A184" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E184" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G184" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H184" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I184" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J184" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K184" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L184" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:12">
+      <x:c r="A185" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F185" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G185" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H185" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I185" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J185" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K185" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L185" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:12">
+      <x:c r="A186" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F186" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G186" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H186" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I186" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J186" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K186" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L186" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:12">
+      <x:c r="A187" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E187" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F187" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G187" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H187" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I187" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J187" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K187" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L187" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:12">
+      <x:c r="A188" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F188" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G188" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H188" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I188" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J188" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K188" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L188" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:12">
+      <x:c r="A189" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E189" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F189" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G189" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H189" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I189" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J189" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K189" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L189" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:12">
+      <x:c r="A190" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F190" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G190" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H190" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I190" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J190" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K190" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L190" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:12">
+      <x:c r="A191" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E191" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F191" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G191" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H191" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I191" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J191" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K191" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L191" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:12">
+      <x:c r="A192" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F192" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G192" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H192" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I192" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J192" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K192" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L192" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:12">
+      <x:c r="A193" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E193" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F193" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G193" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H193" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I193" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J193" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K193" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L193" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:12">
+      <x:c r="A194" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F194" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G194" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H194" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I194" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J194" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K194" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L194" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:12">
+      <x:c r="A195" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E195" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F195" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G195" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H195" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I195" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J195" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K195" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L195" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:12">
+      <x:c r="A196" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E196" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F196" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G196" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H196" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I196" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J196" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K196" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L196" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:12">
+      <x:c r="A197" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E197" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F197" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G197" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H197" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I197" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J197" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K197" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L197" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:12">
+      <x:c r="A198" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E198" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F198" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G198" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H198" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I198" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J198" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K198" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L198" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:12">
+      <x:c r="A199" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E199" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F199" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G199" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H199" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I199" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J199" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K199" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L199" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:12">
+      <x:c r="A200" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E200" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F200" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G200" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H200" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I200" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J200" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K200" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L200" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:12">
+      <x:c r="A201" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E201" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F201" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G201" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H201" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I201" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J201" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K201" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L201" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:12">
+      <x:c r="A202" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E202" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F202" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G202" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H202" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I202" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J202" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K202" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L202" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:12">
+      <x:c r="A203" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D203" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E203" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F203" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G203" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H203" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I203" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J203" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K203" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L203" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:12">
+      <x:c r="A204" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E204" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F204" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G204" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H204" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I204" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J204" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K204" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L204" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:12">
+      <x:c r="A205" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E205" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F205" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G205" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H205" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I205" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J205" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K205" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L205" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:12">
+      <x:c r="A206" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E206" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F206" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G206" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H206" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I206" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J206" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K206" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L206" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:12">
+      <x:c r="A207" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E207" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F207" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G207" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H207" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I207" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J207" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K207" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L207" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:12">
+      <x:c r="A208" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E208" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F208" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G208" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H208" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I208" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J208" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K208" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L208" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:12">
+      <x:c r="A209" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D209" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E209" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F209" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G209" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H209" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I209" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J209" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K209" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L209" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:12">
+      <x:c r="A210" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E210" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F210" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G210" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H210" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I210" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J210" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K210" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L210" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:12">
+      <x:c r="A211" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D211" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E211" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F211" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G211" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H211" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I211" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J211" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K211" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L211" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:12">
+      <x:c r="A212" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F212" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G212" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H212" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I212" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J212" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K212" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L212" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:12">
+      <x:c r="A213" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D213" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E213" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F213" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G213" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H213" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I213" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J213" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K213" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L213" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:12">
+      <x:c r="A214" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E214" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F214" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G214" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H214" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I214" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J214" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K214" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L214" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:12">
+      <x:c r="A215" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D215" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E215" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F215" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G215" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H215" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I215" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J215" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K215" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L215" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:12">
+      <x:c r="A216" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E216" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F216" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G216" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H216" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I216" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J216" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K216" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L216" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:12">
+      <x:c r="A217" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E217" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F217" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G217" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H217" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I217" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J217" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K217" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L217" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:12">
+      <x:c r="A218" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D218" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E218" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F218" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G218" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H218" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I218" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J218" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K218" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L218" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:12">
+      <x:c r="A219" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E219" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F219" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G219" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H219" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I219" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J219" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K219" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L219" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:12">
+      <x:c r="A220" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E220" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F220" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G220" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H220" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I220" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J220" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K220" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L220" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:12">
+      <x:c r="A221" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D221" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E221" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F221" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G221" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H221" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I221" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J221" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K221" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L221" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:12">
+      <x:c r="A222" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E222" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F222" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G222" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H222" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I222" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J222" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K222" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L222" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:12">
+      <x:c r="A223" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D223" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E223" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F223" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G223" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H223" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I223" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J223" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K223" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L223" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:12">
+      <x:c r="A224" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E224" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F224" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G224" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H224" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I224" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J224" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K224" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L224" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:12">
+      <x:c r="A225" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D225" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E225" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F225" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G225" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H225" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I225" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J225" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K225" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L225" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:12">
+      <x:c r="A226" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E226" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F226" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G226" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H226" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I226" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J226" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K226" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L226" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:12">
+      <x:c r="A227" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D227" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E227" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F227" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G227" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H227" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I227" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J227" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K227" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L227" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:12">
+      <x:c r="A228" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B228" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C228" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D228" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E228" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F228" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G228" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H228" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I228" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J228" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K228" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L228" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:12">
+      <x:c r="A229" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B229" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C229" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D229" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E229" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F229" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G229" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H229" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I229" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J229" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K229" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L229" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:12">
+      <x:c r="A230" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B230" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C230" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D230" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E230" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F230" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G230" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H230" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I230" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J230" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K230" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="L230" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:12">
+      <x:c r="A231" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B231" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C231" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D231" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E231" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F231" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G231" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H231" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I231" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J231" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K231" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L231" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
